--- a/api/templates/rif_resistance_rate/uk.xlsx
+++ b/api/templates/rif_resistance_rate/uk.xlsx
@@ -1,43 +1,70 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25629"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\ahernandez\repos\aspect\api\templates\rif_resistance_rate\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23E309EF-FE51-4D52-8DE2-90656BF6D192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176"/>
   </bookViews>
   <sheets>
-    <sheet name="Звіт про опір РІФ" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Звіт про опір РІФ" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="totalDetected1">'Звіт про опір РІФ'!$E$9</definedName>
-    <definedName name="totalDetected2" localSheetId="0">'Звіт про опір РІФ'!$G$9</definedName>
     <definedName name="totalDetected2">'Звіт про опір РІФ'!$F$9</definedName>
   </definedNames>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+  <si>
+    <t>Звіт про опір РІФ</t>
+  </si>
+  <si>
+    <t>Дати: &lt;Dates&gt;</t>
+  </si>
+  <si>
+    <t>Області: &lt;States&gt;</t>
+  </si>
+  <si>
+    <t>Райони: &lt;Lgas&gt;</t>
+  </si>
+  <si>
+    <t>Сайти: &lt;Sites&gt;</t>
+  </si>
   <si>
     <t>&lt;Table&gt;</t>
   </si>
   <si>
+    <t>Пристрої</t>
+  </si>
+  <si>
+    <t>Сайт</t>
+  </si>
+  <si>
+    <t>Райони</t>
+  </si>
+  <si>
+    <t>Загальні тести</t>
+  </si>
+  <si>
+    <t>Виявлений MTB</t>
+  </si>
+  <si>
+    <t>Виявлений опір RIF</t>
+  </si>
+  <si>
+    <t>Швидкість опору RIF</t>
+  </si>
+  <si>
     <t>&lt;name&gt;</t>
   </si>
   <si>
+    <t>&lt;siteName&gt;</t>
+  </si>
+  <si>
     <t>&lt;state&gt;</t>
   </si>
   <si>
@@ -54,81 +81,48 @@
   </si>
   <si>
     <t>&lt;rifResistanceRate&gt;</t>
-  </si>
-  <si>
-    <t>Звіт про опір РІФ</t>
-  </si>
-  <si>
-    <t>Дати: &lt;Dates&gt;</t>
-  </si>
-  <si>
-    <t>Райони: &lt;Lgas&gt;</t>
-  </si>
-  <si>
-    <t>Сайти: &lt;Sites&gt;</t>
-  </si>
-  <si>
-    <t>Пристрої</t>
-  </si>
-  <si>
-    <t>Загальні тести</t>
-  </si>
-  <si>
-    <t>Виявлений MTB</t>
-  </si>
-  <si>
-    <t>Виявлений опір RIF</t>
-  </si>
-  <si>
-    <t>Швидкість опору RIF</t>
-  </si>
-  <si>
-    <t>Райони</t>
-  </si>
-  <si>
-    <t>Області: &lt;States&gt;</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <charset val="1"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="12"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
+      <charset val="204"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="16"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <charset val="204"/>
       <color rgb="FF000000"/>
+      <family val="2"/>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <family val="2"/>
       <sz val="12"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
     </font>
   </fonts>
   <fills count="3">
@@ -154,164 +148,72 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="medium"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="9" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF3CC0DD"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -619,102 +521,120 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr defaultRowHeight="15.6" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" defaultColWidth="11" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="39.09765625" customWidth="1"/>
-    <col min="2" max="2" width="29.09765625" customWidth="1"/>
-    <col min="3" max="3" width="27.09765625" customWidth="1"/>
-    <col min="4" max="4" width="13.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.59765625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.59765625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.3984375" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="29.09765625" customWidth="1"/>
+    <col min="4" max="4" width="27.09765625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.3984375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.59765625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5" style="2" customWidth="1"/>
+    <col min="8" max="8" width="15.59765625" customWidth="1"/>
     <col min="9" max="9" width="14.3984375" customWidth="1"/>
     <col min="11" max="11" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.4">
+    <row r="1" ht="21" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" ht="16.2" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" ht="33.75" customHeight="1" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="8" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="14" t="s">
+      <c r="F8" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="13" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" s="9" customFormat="1" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>6</v>
-      </c>
       <c r="G9" s="13" t="s">
-        <v>7</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="2"/>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/api/templates/rif_resistance_rate/uk.xlsx
+++ b/api/templates/rif_resistance_rate/uk.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10531"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE4CD8A0-49A1-E647-A6E4-E32A770A4A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Звіт про опір РІФ" state="visible" r:id="rId4"/>
+    <sheet name="Звіт про опір РІФ" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="totalDetected1">'Звіт про опір РІФ'!$E$9</definedName>
@@ -86,43 +87,43 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
-      <color rgb="FF000000"/>
-      <family val="2"/>
-      <sz val="12"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="204"/>
-      <color rgb="FF000000"/>
-      <family val="2"/>
-      <sz val="16"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="204"/>
-      <color rgb="FF000000"/>
-      <family val="2"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <charset val="1"/>
-      <family val="2"/>
       <sz val="12"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -148,24 +149,48 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium"/>
-      <right style="medium"/>
-      <top style="medium"/>
-      <bottom style="medium"/>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="medium"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -201,9 +226,7 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -521,60 +544,60 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultRowHeight="15.6" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" defaultColWidth="11" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="39.09765625" customWidth="1"/>
-    <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="29.09765625" customWidth="1"/>
-    <col min="4" max="4" width="27.09765625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.3984375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.59765625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="39.1640625" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="29.1640625" customWidth="1"/>
+    <col min="4" max="4" width="27.1640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.33203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.6640625" style="1" customWidth="1"/>
     <col min="7" max="7" width="14.5" style="2" customWidth="1"/>
-    <col min="8" max="8" width="15.59765625" customWidth="1"/>
-    <col min="9" max="9" width="14.3984375" customWidth="1"/>
+    <col min="8" max="8" width="15.6640625" customWidth="1"/>
+    <col min="9" max="9" width="14.33203125" customWidth="1"/>
     <col min="11" max="11" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" ht="16.2" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="16.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" ht="33.75" customHeight="1" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" s="6" customFormat="1" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>6</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>7</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>8</v>
@@ -595,20 +618,20 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F9" s="13" t="s">
@@ -621,20 +644,16 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
+    <row r="10" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="G10" s="1"/>
       <c r="H10" s="2"/>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
+    <row r="11" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="G11" s="1"/>
       <c r="H11" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/api/templates/rif_resistance_rate/uk.xlsx
+++ b/api/templates/rif_resistance_rate/uk.xlsx
@@ -1,14 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10531"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE4CD8A0-49A1-E647-A6E4-E32A770A4A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680"/>
   </bookViews>
   <sheets>
-    <sheet name="Звіт про опір РІФ" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Звіт про опір РІФ" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="totalDetected1">'Звіт про опір РІФ'!$E$9</definedName>
@@ -19,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
   <si>
     <t>Звіт про опір РІФ</t>
   </si>
@@ -36,15 +35,18 @@
     <t>Сайти: &lt;Sites&gt;</t>
   </si>
   <si>
+    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
+  </si>
+  <si>
     <t>&lt;Table&gt;</t>
   </si>
   <si>
+    <t>Сайт</t>
+  </si>
+  <si>
     <t>Пристрої</t>
   </si>
   <si>
-    <t>Сайт</t>
-  </si>
-  <si>
     <t>Райони</t>
   </si>
   <si>
@@ -60,10 +62,10 @@
     <t>Швидкість опору RIF</t>
   </si>
   <si>
+    <t>&lt;siteName&gt;</t>
+  </si>
+  <si>
     <t>&lt;name&gt;</t>
-  </si>
-  <si>
-    <t>&lt;siteName&gt;</t>
   </si>
   <si>
     <t>&lt;state&gt;</t>
@@ -87,43 +89,43 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <charset val="1"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="12"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
+      <charset val="204"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="16"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
     </font>
     <font>
+      <charset val="204"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <family val="2"/>
       <sz val="12"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -149,48 +151,24 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="medium"/>
+      <right style="thin"/>
+      <top style="medium"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="medium"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -544,9 +522,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.5" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="11" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="39.1640625" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -560,100 +538,105 @@
     <col min="11" max="11" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="21" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" ht="16" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" ht="16" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" ht="16" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+    <row r="5" ht="17" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="16.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="17" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" ht="16.25" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" s="6" customFormat="1" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" ht="33.75" customHeight="1" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G10" s="1"/>
       <c r="H10" s="2"/>
     </row>
-    <row r="11" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" ht="16" customHeight="1" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G11" s="1"/>
       <c r="H11" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/api/templates/rif_resistance_rate/uk.xlsx
+++ b/api/templates/rif_resistance_rate/uk.xlsx
@@ -185,9 +185,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>

--- a/api/templates/rif_resistance_rate/uk.xlsx
+++ b/api/templates/rif_resistance_rate/uk.xlsx
@@ -35,7 +35,7 @@
     <t>Сайти: &lt;Sites&gt;</t>
   </si>
   <si>
-    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
+    <t>Виведені з експлуатації пристрої: &lt;DecommissionedDevices&gt;</t>
   </si>
   <si>
     <t>&lt;Table&gt;</t>
@@ -185,7 +185,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
